--- a/operator-email-addresses.xlsx
+++ b/operator-email-addresses.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\twood.TF\Documents\Github\Sales Order Processing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\twood.TF\Documents\Github\Sales-Order-Processing-BCB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B19E8CE3-FD37-4D01-AFE8-A2479140AAFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{365484A1-D32C-4FC9-A51D-5166978907D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Operator</t>
   </si>
@@ -43,6 +43,12 @@
   </si>
   <si>
     <t>rebeccaw@boconceptadelaide.com.au</t>
+  </si>
+  <si>
+    <t>ryans@boconceptbrisbane.com.au</t>
+  </si>
+  <si>
+    <t>Ryan Stevens</t>
   </si>
 </sst>
 </file>
@@ -371,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.26953125" bestFit="1" customWidth="1"/>
@@ -402,10 +408,19 @@
         <v>5</v>
       </c>
     </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{D2EB214D-7767-4FF8-91B4-605B5FFC154E}"/>
     <hyperlink ref="B3" r:id="rId2" xr:uid="{3A75B77C-67E9-4DEA-9C50-073FB35C8759}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{9F494FD5-B746-4FC8-8538-2804693D3493}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
